--- a/experiment/HAT_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/HAT_bestx4/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.03</v>
+        <v>23.04</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5337</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.21</v>
+        <v>26.09</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7565</v>
+        <v>0.7548</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.39</v>
+        <v>25.4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.637</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.23</v>
+        <v>26.24</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5762</v>
+        <v>0.5759</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.54</v>
+        <v>23.57</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7383</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.94</v>
+        <v>32.95</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7955</v>
+        <v>0.7957</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.36</v>
+        <v>28.37</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8216</v>
+        <v>0.8224</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.64</v>
+        <v>33.69</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9186</v>
+        <v>0.9193</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.64</v>
+        <v>32.65</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8666</v>
+        <v>0.8672</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.37</v>
+        <v>27.36</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7502</v>
+        <v>0.7503</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.98</v>
+        <v>33.06</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9457</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.28</v>
+        <v>34.32</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8807</v>
+        <v>0.8811</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.67</v>
+        <v>26.72</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9508</v>
+        <v>0.9516</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.38</v>
+        <v>27.41</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7779</v>
+        <v>0.7783</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.62</v>
+        <v>28.63</v>
       </c>
       <c r="C16" t="n">
-        <v>0.782</v>
+        <v>0.7825</v>
       </c>
     </row>
   </sheetData>
